--- a/data_out/country_spreadsheets/Lithuania.xlsx
+++ b/data_out/country_spreadsheets/Lithuania.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>93.38</v>
       </c>
+      <c r="X2" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>118.81</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>168.65</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>249.23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>159.35</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>146.49</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>93.38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>183.33</v>
       </c>
+      <c r="X3" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>191.56</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>274.75</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>164.16</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>183.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>214.65</v>
       </c>
+      <c r="X4" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>157.66</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>147.91</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>256.01</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>145.03</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>262.22</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>255.18</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>214.65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>50.28</v>
       </c>
+      <c r="X5" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>65.33</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>124.65</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>123.93</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>50.28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>232.86</v>
       </c>
+      <c r="X6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>146.47</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>270.18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>152.37</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>85.56</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>227.85</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>276.35</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>232.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>150.75</v>
       </c>
+      <c r="X7" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>196.71</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>131.46</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>69.16</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>178.01</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>150.75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>120.04</v>
       </c>
+      <c r="X8" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>120.96</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>191.83</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>215.22</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>120.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>145.57</v>
       </c>
+      <c r="X9" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>209.29</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>167.71</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>88.76000000000001</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>171.34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>215</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>145.57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>146.24</v>
       </c>
+      <c r="X10" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>185.59</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>123.76</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>187.01</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>188.09</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>146.24</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1312,6 +1856,57 @@
         <v>81.41</v>
       </c>
       <c r="W11" t="n">
+        <v>71.94</v>
+      </c>
+      <c r="X11" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>160.44</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>172.78</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>113.27</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>109.51</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="AN11" t="n">
         <v>71.94</v>
       </c>
     </row>
